--- a/data/trans_orig/KIDM_C_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_1_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>21308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28421</t>
+          <t>28365</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146562</t>
+          <t>146327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156009</t>
+          <t>156136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189164</t>
+          <t>188370</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199667</t>
+          <t>199190</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>339344</t>
+          <t>339494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353751</t>
+          <t>353603</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33202</t>
+          <t>33166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43670</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51843</t>
+          <t>51788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>80214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89286</t>
+          <t>89694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>33181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>191806</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204795</t>
+          <t>204302</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>251394</t>
+          <t>252686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265435</t>
+          <t>265844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>450122</t>
+          <t>449438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>467845</t>
+          <t>467985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
